--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -11,8 +11,7 @@
     <sheet name="diagnostics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="manual_required" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="source_catalogue" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="source_links" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,7 +698,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Singapore overall unemployment rate for Mar-26 / 1Q 2026; reviewed static row.</t>
+          <t>Singapore overall unemployment rate for Mar-26 / 1Q 2026; reviewed row.</t>
         </is>
       </c>
     </row>
@@ -734,59 +733,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Official / API</t>
+          <t>Official / Reviewed</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fetched from C&amp;SD Table 510-60001 JSON API; sv=CC_CM_1920; period=202605; figure column.</t>
+          <t>Reviewed row. Replace with live C&amp;SD Table 510-60001 fetch when confirmed in macro fetcher runtime.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Fetched Malaysia headline CPI inflation YoY from OpenDOSM official CSV; filtered division=overall.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -800,7 +799,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -809,7 +808,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>ISM Manufacturing PMI / seed fallback</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -826,7 +825,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -840,7 +839,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50.4</v>
+        <v>51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -849,7 +848,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
+          <t>SIPMM Singapore Manufacturing PMI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -866,7 +865,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -880,7 +879,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -889,7 +888,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NBS Manufacturing PMI</t>
+          <t>S&amp;P Global Hong Kong SAR PMI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -906,7 +905,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,7 +919,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -929,7 +928,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+          <t>NBS Manufacturing PMI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -946,38 +945,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Seed fallback; review before active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>PMI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>50.4</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>au Jibun Bank Japan Manufacturing PMI</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Seed fallback; review before active use.</t>
         </is>
@@ -994,584 +1033,646 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>run_utc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>indicator</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>source_name</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>endpoint</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>generated_at</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:38Z</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Inflation</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>FRED CPIAUCSL YoY</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4.167%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-05-01 = 4.167%</t>
-        </is>
+      <c r="F2" t="n">
+        <v>4.167</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Computed CPI YoY from FRED CPIAUCSL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=CPIAUCSL</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:38Z</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Unemployment</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>FRED UNRATE</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4.3</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-01 = 4.3%</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Fetched FRED UNRATE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=UNRATE</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:39Z</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>FRED ICSA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>226</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-06-13 = 226.0k</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Fetched FRED ICSA and converted to thousands</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=ICSA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:39Z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Rates</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>FRED DGS10</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>4.5</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-23 = 4.5%</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Fetched FRED DGS10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=DGS10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:39Z</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Inflation</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>SingStat CPI</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>reviewed_static</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Reviewed row retained</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Reviewed static row</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:39Z</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Unemployment</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>MOM / SingStat unemployment</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>reviewed_static</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Reviewed row retained</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Reviewed static row</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>2026-06-25T08:37:39Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Inflation</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OpenDOSM headline CPI cpi_2d</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HTTP Error 404: Not Found</t>
-        </is>
+          <t>C&amp;SD Table 510-60001 Composite CPI YoY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://api.data.gov.my/data-catalogue?id=cpi_2d&amp;limit=5000</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+          <t>Reviewed row</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>2026-06-25T08:37:40Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Inflation</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>C&amp;SD Table 510-60001 Composite CPI YoY</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2.0%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Fetched dynamically for 2026-05-01</t>
-        </is>
+      <c r="F9" t="n">
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.censtatd.gov.hk/api/get.php?id=510-60001&amp;lang=en&amp;full_series=1</t>
+          <t>Latest division=overall inflation_yoy = 2.0 for 2026-05-01</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-06-25T02:47:24Z</t>
+          <t>https://storage.dosm.gov.my/cpi/cpi_2d_inflation.csv</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>54</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>OpenDOSM unemployment</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Could not identify unemployment date/value columns; columns=['lf', 'date', 'p_rate', 'u_rate', 'ep_ratio', 'lf_outside', 'lf_employed', 'lf_unemployed']</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-06-25T02:47:24Z</t>
+          <t>https://api.data.gov.my/opendosm?id=lfs_month&amp;limit=50000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>Rates</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>51</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+          <t>BNM OPR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Policy: Malaysia rates handled by live adapter, not monthly macro pack.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>PMI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ISM Manufacturing PMI / seed fallback</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+      <c r="F12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>PMI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NBS Manufacturing PMI</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>SIPMM Singapore Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+      <c r="F13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>PMI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>S&amp;P Global Hong Kong SAR PMI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+      <c r="F14" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:41Z</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NBS Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-25T08:37:41Z</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-25T08:37:41Z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>PMI</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>au Jibun Bank Japan Manufacturing PMI</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F17" t="n">
         <v>50.4</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1590,44 +1691,44 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>run_utc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>market</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>indicator</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>reason</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>suggested_action</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-06-25T08:37:41Z</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>MY</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OpenDOSM CPI fetch failed: HTTP Error 404: Not Found</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Review latest official value</t>
+          <t>OpenDOSM unemployment fetch failed: Could not identify unemployment date/value columns; columns=['lf', 'date', 'p_rate', 'u_rate', 'ep_ratio', 'lf_outside', 'lf_employed', 'lf_unemployed']</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,20 +1764,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>endpoint_or_url</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>endpoint</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1685,118 +1781,103 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rates</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MAS SORA</t>
+          <t>FRED CPIAUCSL YoY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MAS open search/API route in Streamlit live adapter</t>
+          <t>Official / API</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>https://fred.stlouisfed.org/series/CPIAUCSL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Decision 1; excluded from active macro_data.csv.</t>
+          <t>Computed YoY from CPI index</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rates</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BNM OPR</t>
+          <t>FRED UNRATE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BNM OpenAPI live adapter</t>
+          <t>Official / API</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Policy/daily availability</t>
+          <t>https://fred.stlouisfed.org/series/UNRATE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Decision 2; excluded from active macro_data.csv.</t>
+          <t>US unemployment rate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rates</t>
+          <t>Claims</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HKMA HIBOR / HKD rates</t>
+          <t>FRED ICSA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HKMA Open API live adapter</t>
+          <t>Official / API</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>https://fred.stlouisfed.org/series/ICSA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Decision 3; excluded from active macro_data.csv.</t>
+          <t>US initial claims</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1806,71 +1887,57 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOJ FM01 overnight call rate</t>
+          <t>FRED DGS10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BOJ Time-Series API live adapter</t>
+          <t>Official / API</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>https://fred.stlouisfed.org/series/DGS10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Decision 4; excluded from active macro_data.csv.</t>
+          <t>US 10-year Treasury</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unemployment</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OpenDOSM u_rate</t>
+          <t>SingStat CPI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OpenDOSM API live adapter</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
+          <t>Official / Reviewed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Decision 5; live API due unreliable monthly pack route.</t>
+          <t>Reviewed static row pending full integration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1880,64 +1947,46 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DBnomics / STATJP</t>
+          <t>MOM / SingStat unemployment</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DBnomics API live adapter</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
+          <t>Official / Reviewed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Decision 6; live API due unreliable monthly pack route.</t>
+          <t>Reviewed static row</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inflation</t>
+          <t>Rates</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DBnomics / STATJP CPI</t>
+          <t>SG SORA live redistributor only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DBnomics API live adapter</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
+          <t>Live app only</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Decision 7; live API due unreliable monthly pack route.</t>
+          <t>Excluded from macro pack</t>
         </is>
       </c>
     </row>
@@ -1959,29 +2008,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.censtatd.gov.hk/api/get.php?id=510-60001&amp;lang=en&amp;full_series=1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
+          <t>Official / Reviewed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>sv=CC_CM_1920; period=YYYYMM; value=figure.</t>
+          <t>Reviewed/live integration dependent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1991,34 +2031,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FRED CPIAUCSL YoY</t>
+          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=CPIAUCSL</t>
+          <t>Official CSV</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>https://storage.dosm.gov.my/cpi/cpi_2d_inflation.csv</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Computed YoY from CPI index.</t>
+          <t>Filter division=overall; use inflation_yoy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2028,71 +2063,57 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FRED UNRATE</t>
+          <t>OpenDOSM unemployment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=UNRATE</t>
+          <t>Official / API</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>https://api.data.gov.my/opendosm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Latest value.</t>
+          <t>Tolerant helper; manual if unavailable</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Claims</t>
+          <t>Rates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FRED ICSA</t>
+          <t>BNM OPR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=ICSA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
+          <t>Live app only</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Converted to thousands.</t>
+          <t>Excluded from macro pack if live policy applies</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2102,27 +2123,46 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FRED DGS10</t>
+          <t>BOJ FM01 STRDCLUCON CSV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=DGS10</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
+          <t>Live app only</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>US 10-year Treasury constant maturity.</t>
+          <t>Excluded from macro pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Seed rows</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Review before active use</t>
         </is>
       </c>
     </row>
@@ -2137,36 +2177,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>generated_utc</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
-        <is>
-          <t>indicator</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>endpoint_or_url</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -2175,458 +2195,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>2026-06-25T08:37:41Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MAS SORA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MAS open search/API route in Streamlit live adapter</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Decision 1; excluded from active macro_data.csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BNM OPR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BNM OpenAPI live adapter</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Decision 2; excluded from active macro_data.csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HKMA HIBOR / HKD rates</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HKMA Open API live adapter</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Decision 3; excluded from active macro_data.csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>BOJ FM01 overnight call rate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BOJ Time-Series API live adapter</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Live API only</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Decision 4; excluded from active macro_data.csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Unemployment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OpenDOSM u_rate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>OpenDOSM API live adapter</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Decision 5; live API due unreliable monthly pack route.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Unemployment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DBnomics / STATJP</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DBnomics API live adapter</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Decision 6; live API due unreliable monthly pack route.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DBnomics / STATJP CPI</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DBnomics API live adapter</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Live API exception</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Decision 7; live API due unreliable monthly pack route.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>C&amp;SD Table 510-60001 Composite CPI YoY</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.censtatd.gov.hk/api/get.php?id=510-60001&amp;lang=en&amp;full_series=1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>sv=CC_CM_1920; period=YYYYMM; value=figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FRED CPIAUCSL YoY</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=CPIAUCSL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Computed YoY from CPI index.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Unemployment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FRED UNRATE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=UNRATE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Latest value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Claims</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FRED ICSA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=ICSA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Converted to thousands.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rates</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>FRED DGS10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/graph/fredgraph.csv?id=DGS10</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Macro pack official API</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>US 10-year Treasury constant maturity.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-25T02:47:24Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>APAC Rates SG/MY/HK/JP are live API only and removed from active macro_data.csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hk_inflation</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HK Inflation fetched dynamically from C&amp;SD Table 510-60001 JSON API using sv=CC_CM_1920.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>decisions_5_7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MY unemployment, JP unemployment, JP inflation remain live API exceptions due unreliable monthly macro pack route.</t>
+          <t>Global20Engine macro pack generated. MY Inflation uses OpenDOSM official CSV cpi_2d_inflation, division=overall, inflation_yoy. SG and JP rates are excluded from macro pack active monthly fetch path and handled by live adapters in main app.</t>
         </is>
       </c>
     </row>

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -555,11 +555,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:38Z</t>
+          <t>2026-06-25T14:13:04Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:38Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:39Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:39Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:39Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:39Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:39Z</t>
+          <t>2026-06-25T14:13:05Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:40Z</t>
+          <t>2026-06-25T14:13:06Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T08:37:41Z</t>
+          <t>2026-06-25T14:13:07Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1081,7 +1081,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:04Z</t>
+          <t>2026-06-25T15:02:48Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:48Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:48Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:49Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:49Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:49Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:05Z</t>
+          <t>2026-06-25T15:02:49Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:06Z</t>
+          <t>2026-06-25T15:02:50Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T14:13:07Z</t>
+          <t>2026-06-25T15:02:51Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1081,7 +1081,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:48Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:48Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:48Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:49Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:49Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:49Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:49Z</t>
+          <t>2026-06-25T15:48:29Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:50Z</t>
+          <t>2026-06-25T15:48:31Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1569,7 +1569,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2195,7 +2195,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:02:51Z</t>
+          <t>2026-06-25T15:48:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,21 +745,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inflation</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -768,144 +768,144 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
+          <t>HK Government / C&amp;SD unemployment press release</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>Official / Parsed</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fetched Malaysia headline CPI inflation YoY from OpenDOSM official CSV; filtered division=overall.</t>
+          <t>Parsed from official HK unemployment press release; period=March - May 2026.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Fetched Malaysia headline CPI inflation YoY from OpenDOSM official CSV; filtered division=overall.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>Statistics Bureau of Japan latest indicators / CPI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Official / Parsed</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed Japan CPI YoY from Statistics Bureau latest indicators; period=May 2026.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50.4</v>
+        <v>2.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
+          <t>Statistics Bureau of Japan latest indicators / Labour Force Survey</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Official / Parsed</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed Japan unemployment rate from Statistics Bureau latest indicators; period=April 2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NBS Manufacturing PMI</t>
+          <t>ISM Manufacturing PMI / seed fallback</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+          <t>SIPMM Singapore Manufacturing PMI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1008,15 +1008,135 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>S&amp;P Global Hong Kong SAR PMI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Seed fallback; review before active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NBS Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Seed fallback; review before active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Seed fallback; review before active use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>au Jibun Bank Japan Manufacturing PMI</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Seed fallback; review before active use.</t>
         </is>
@@ -1033,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,7 +1201,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1121,7 +1241,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1161,7 +1281,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1201,7 +1321,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1241,7 +1361,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1277,7 +1397,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1313,7 +1433,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:29Z</t>
+          <t>2026-06-25T16:02:51Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1349,22 +1469,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:31Z</t>
+          <t>2026-06-25T16:02:52Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inflation</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
+          <t>HK Government / C&amp;SD unemployment press release</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1373,23 +1493,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Latest division=overall inflation_yoy = 2.0 for 2026-05-01</t>
+          <t>Parsed HK unemployment 3.7% for March - May 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://storage.dosm.gov.my/cpi/cpi_2d_inflation.csv</t>
+          <t>https://www.info.gov.hk/gia/general/202606/16/P2026061600318.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:53Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1399,35 +1519,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unemployment</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OpenDOSM unemployment</t>
+          <t>OpenDOSM storage CSV cpi_2d_inflation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Could not identify unemployment date/value columns; columns=['lf', 'date', 'p_rate', 'u_rate', 'ep_ratio', 'lf_outside', 'lf_employed', 'lf_unemployed']</t>
+          <t>Latest division=overall inflation_yoy = 2.0 for 2026-05-01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://api.data.gov.my/opendosm?id=lfs_month&amp;limit=50000</t>
+          <t>https://storage.dosm.gov.my/cpi/cpi_2d_inflation.csv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1437,59 +1559,61 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rates</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BNM OPR</t>
+          <t>OpenDOSM unemployment</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Policy: Malaysia rates handled by live adapter, not monthly macro pack.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Could not identify unemployment date/value columns; columns=['lf', 'date', 'p_rate', 'u_rate', 'ep_ratio', 'lf_outside', 'lf_employed', 'lf_unemployed']</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://api.data.gov.my/opendosm?id=lfs_month&amp;limit=50000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Rates</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>BNM OPR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>54</v>
-      </c>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
+          <t>Policy: Malaysia rates handled by live adapter, not monthly macro pack.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1497,84 +1621,92 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>Statistics Bureau of Japan latest indicators / CPI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Parsed Japan CPI YoY 1.5% for May 2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.stat.go.jp/english/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
+          <t>Statistics Bureau of Japan latest indicators / Labour Force Survey</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>50.4</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Parsed Japan unemployment 2.5% for April 2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.stat.go.jp/english/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1584,7 +1716,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NBS Manufacturing PMI</t>
+          <t>ISM Manufacturing PMI / seed fallback</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1593,7 +1725,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1605,12 +1737,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1620,7 +1752,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+          <t>SIPMM Singapore Manufacturing PMI</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1629,7 +1761,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1641,12 +1773,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1656,7 +1788,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>au Jibun Bank Japan Manufacturing PMI</t>
+          <t>S&amp;P Global Hong Kong SAR PMI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1673,6 +1805,114 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-25T16:02:54Z</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NBS Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-25T16:02:54Z</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-25T16:02:54Z</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>au Jibun Bank Japan Manufacturing PMI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Seed fallback row</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1713,7 +1953,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2195,7 +2435,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T15:48:32Z</t>
+          <t>2026-06-25T16:02:54Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -595,11 +595,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:51Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:52Z</t>
+          <t>2026-06-26T01:37:16Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:53Z</t>
+          <t>2026-06-26T01:37:17Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:18Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:18Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:18Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25T16:02:54Z</t>
+          <t>2026-06-26T01:37:19Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,7 +915,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -928,17 +928,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>ISM Manufacturing PMI via PRNewswire release</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Parsed / Release</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed PMI from source; period=May 2026.</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -968,17 +968,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>SIPMM Singapore Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Parsed / Secondary</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed PMI from source; period=May 2026.</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1008,24 +1008,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
+          <t>S&amp;P Global Hong Kong SAR PMI via Trading Economics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Parsed / Secondary</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed PMI from source; period=May 2026.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1048,24 +1048,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NBS Manufacturing PMI</t>
+          <t>S&amp;P Global Malaysia Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Parsed / Secondary</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed PMI from source; period=May 2026.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49.9</v>
+        <v>54.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1088,57 +1088,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+          <t>S&amp;P Global Japan Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>Parsed / Secondary</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Seed fallback; review before active use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PMI</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>au Jibun Bank Japan Manufacturing PMI</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Seed</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Seed fallback; review before active use.</t>
+          <t>Parsed PMI from source; period=June 2026.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1201,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1241,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1281,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1321,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1361,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1397,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1433,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1469,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:16Z</t>
+          <t>2026-06-26T02:15:04Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1509,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:17Z</t>
+          <t>2026-06-26T02:15:06Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1549,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:18Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1587,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:18Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1621,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1661,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1701,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1716,12 +1676,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMI / seed fallback</t>
+          <t>ISM Manufacturing PMI via PRNewswire release</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1729,15 +1689,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Parsed PMI 54.0 for May 2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/manufacturing-pmi-at-54-may-2026-ism-manufacturing-pmi-report-302786165.html</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1752,12 +1716,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SIPMM Singapore Manufacturing PMI</t>
+          <t>SIPMM Singapore Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1765,15 +1729,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Parsed PMI 51.0 for May 2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/singapore/manufacturing-pmi</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:08Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1788,12 +1756,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S&amp;P Global Hong Kong SAR PMI</t>
+          <t>S&amp;P Global Hong Kong SAR PMI via Trading Economics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1801,20 +1769,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Parsed PMI 50.4 for May 2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/hong-kong/manufacturing-pmi</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:08Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1824,33 +1796,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NBS Manufacturing PMI</t>
+          <t>S&amp;P Global Malaysia Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Parsed PMI 49.9 for May 2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/malaysia/manufacturing-pmi</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:08Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1860,59 +1836,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI</t>
+          <t>S&amp;P Global Japan Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>success</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>49.9</v>
+        <v>54.9</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-26T01:37:19Z</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PMI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>au Jibun Bank Japan Manufacturing PMI</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Seed fallback row</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Parsed PMI 54.9 for June 2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://tradingeconomics.com/japan/manufacturing-pmi</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1953,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:18Z</t>
+          <t>2026-06-26T02:15:07Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2435,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T01:37:19Z</t>
+          <t>2026-06-26T02:15:08Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:04Z</t>
+          <t>2026-06-26T06:34:31Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:06Z</t>
+          <t>2026-06-26T06:34:32Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:34Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:34Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:08Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:08Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:08Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:07Z</t>
+          <t>2026-06-26T06:34:34Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T02:15:08Z</t>
+          <t>2026-06-26T06:34:35Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:31Z</t>
+          <t>2026-06-26T06:38:30Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:32Z</t>
+          <t>2026-06-26T06:38:31Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:34Z</t>
+          <t>2026-06-26T06:38:32Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:34Z</t>
+          <t>2026-06-26T06:38:32Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:34Z</t>
+          <t>2026-06-26T06:38:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:34:35Z</t>
+          <t>2026-06-26T06:38:33Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:30Z</t>
+          <t>2026-06-26T06:55:27Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:31Z</t>
+          <t>2026-06-26T06:55:29Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:32Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:32Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:32Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:38:33Z</t>
+          <t>2026-06-26T06:55:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:27Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:29Z</t>
+          <t>2026-06-26T07:06:30Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T06:55:30Z</t>
+          <t>2026-06-26T07:06:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:36Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:30Z</t>
+          <t>2026-06-26T07:32:37Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:40Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:40Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:40Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:39Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:06:32Z</t>
+          <t>2026-06-26T07:32:40Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:27Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:27Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:27Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:28Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:28Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:28Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:28Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:36Z</t>
+          <t>2026-06-26T07:51:28Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:37Z</t>
+          <t>2026-06-26T07:51:29Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:30Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:30Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:31Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:31Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:31Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:31Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:40Z</t>
+          <t>2026-06-26T07:51:31Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:40Z</t>
+          <t>2026-06-26T07:51:32Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:40Z</t>
+          <t>2026-06-26T07:51:32Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:39Z</t>
+          <t>2026-06-26T07:51:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:32:40Z</t>
+          <t>2026-06-26T07:51:32Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:27Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:27Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:27Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:28Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:28Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:28Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:28Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:28Z</t>
+          <t>2026-06-26T08:04:18Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:29Z</t>
+          <t>2026-06-26T08:04:19Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:30Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:30Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:31Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:31Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:31Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:31Z</t>
+          <t>2026-06-26T08:04:21Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:31Z</t>
+          <t>2026-06-26T08:04:21Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:32Z</t>
+          <t>2026-06-26T08:04:21Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:32Z</t>
+          <t>2026-06-26T08:04:21Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:30Z</t>
+          <t>2026-06-26T08:04:20Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T07:51:32Z</t>
+          <t>2026-06-26T08:04:21Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:18Z</t>
+          <t>2026-06-26T08:16:30Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:19Z</t>
+          <t>2026-06-26T08:16:32Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:21Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:21Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:21Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:21Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:20Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:04:21Z</t>
+          <t>2026-06-26T08:16:33Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:44Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:30Z</t>
+          <t>2026-06-26T08:25:45Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:32Z</t>
+          <t>2026-06-26T08:25:46Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:47Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:47Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:48Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:49Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:47Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:16:33Z</t>
+          <t>2026-06-26T08:25:49Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="macro_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="manual_required" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_catalogue" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_required" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_catalogue" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:44Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:45Z</t>
+          <t>2026-06-26T11:30:31Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:46Z</t>
+          <t>2026-06-26T11:30:33Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:47Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:47Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:48Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:49Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:47Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T08:25:49Z</t>
+          <t>2026-06-26T11:30:36Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:31Z</t>
+          <t>2026-06-26T15:01:23Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:33Z</t>
+          <t>2026-06-26T15:01:25Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:26Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:26Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1855,6 +1855,44 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>https://tradingeconomics.com/japan/manufacturing-pmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-26T15:01:27Z</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PACK</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Manual seed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>macro_seed_inputs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>name 'load_manual_macro_seed' is not defined</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>macro_seed_inputs/</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1935,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:26Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2379,7 +2417,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T11:30:36Z</t>
+          <t>2026-06-26T15:01:27Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +1241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:23Z</t>
+          <t>2026-06-26T15:41:45Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +1469,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:25Z</t>
+          <t>2026-06-26T15:41:47Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:26Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:26Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +1661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:26Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:01:27Z</t>
+          <t>2026-06-26T15:41:50Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,11 +595,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1099,6 +1099,1166 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>Parsed PMI from source; period=June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.678445229681969</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>YoY calculated from CPI index by parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.419698314108242</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>YoY calculated from CPI index by parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1.591511936339529</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>YoY calculated from CPI index by parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.585903083700435</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>YoY calculated from CPI index by parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.755926251097462</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>YoY calculated from CPI index by parser</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unemployment</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Inflation</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>% YoY</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SingStat CPI YoY manual export - All Items</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Manual official seed</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Percent change in CPI over corresponding period of previous year</t>
         </is>
       </c>
     </row>
@@ -1161,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1201,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1241,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1281,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1305,7 +2465,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1321,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1357,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1393,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:45Z</t>
+          <t>2026-06-27T00:04:46Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1469,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:47Z</t>
+          <t>2026-06-27T00:04:48Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1509,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1547,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1581,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1621,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1661,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1701,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1741,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1781,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:52Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1861,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:52Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1881,13 +3041,13 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>accepted</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>name 'load_manual_macro_seed' is not defined</t>
+          <t>manual_macro_rows=29, manual_rate_rows=504</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1935,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:51Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2417,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26T15:41:50Z</t>
+          <t>2026-06-27T00:04:52Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:46Z</t>
+          <t>2026-06-27T08:53:15Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:48Z</t>
+          <t>2026-06-27T08:53:17Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:20Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:20Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:52Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:52Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:51Z</t>
+          <t>2026-06-27T08:53:20Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T00:04:52Z</t>
+          <t>2026-06-27T08:53:21Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:09Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:09Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:15Z</t>
+          <t>2026-06-27T13:27:10Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:17Z</t>
+          <t>2026-06-27T13:27:12Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:20Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:20Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:16Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:16Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:20Z</t>
+          <t>2026-06-27T13:27:15Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T08:53:21Z</t>
+          <t>2026-06-27T13:27:16Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:09Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:09Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:10Z</t>
+          <t>2026-06-27T13:48:12Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:12Z</t>
+          <t>2026-06-27T13:48:14Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:17Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:16Z</t>
+          <t>2026-06-27T13:48:17Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:16Z</t>
+          <t>2026-06-27T13:48:17Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:15Z</t>
+          <t>2026-06-27T13:48:16Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:27:16Z</t>
+          <t>2026-06-27T13:48:17Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:12Z</t>
+          <t>2026-06-27T14:18:19Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:14Z</t>
+          <t>2026-06-27T14:18:20Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:17Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:17Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:17Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:16Z</t>
+          <t>2026-06-27T14:18:23Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T13:48:17Z</t>
+          <t>2026-06-27T14:18:24Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:26Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:26Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:27Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:27Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:27Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:27Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:27Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:19Z</t>
+          <t>2026-06-28T00:10:28Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:20Z</t>
+          <t>2026-06-28T00:10:29Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:31Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:31Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:32Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:32Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:32Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:32Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:32Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:33Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:33Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:33Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:23Z</t>
+          <t>2026-06-28T00:10:31Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T14:18:24Z</t>
+          <t>2026-06-28T00:10:33Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -2321,7 +2321,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:26Z</t>
+          <t>2026-06-28T00:20:16Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:26Z</t>
+          <t>2026-06-28T00:20:16Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:27Z</t>
+          <t>2026-06-28T00:20:17Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:27Z</t>
+          <t>2026-06-28T00:20:18Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:27Z</t>
+          <t>2026-06-28T00:20:18Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:27Z</t>
+          <t>2026-06-28T00:20:18Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:27Z</t>
+          <t>2026-06-28T00:20:18Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:28Z</t>
+          <t>2026-06-28T00:20:18Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:29Z</t>
+          <t>2026-06-28T00:20:20Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2669,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:31Z</t>
+          <t>2026-06-28T00:20:22Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:31Z</t>
+          <t>2026-06-28T00:20:22Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:32Z</t>
+          <t>2026-06-28T00:20:23Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:32Z</t>
+          <t>2026-06-28T00:20:23Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:32Z</t>
+          <t>2026-06-28T00:20:23Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:32Z</t>
+          <t>2026-06-28T00:20:23Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:32Z</t>
+          <t>2026-06-28T00:20:24Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:33Z</t>
+          <t>2026-06-28T00:20:24Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:33Z</t>
+          <t>2026-06-28T00:20:24Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:33Z</t>
+          <t>2026-06-28T00:20:24Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:31Z</t>
+          <t>2026-06-28T00:20:22Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:10:33Z</t>
+          <t>2026-06-28T00:20:24Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/macro_pack_latest/macro_pack.xlsx
+++ b/macro_pack_latest/macro_pack.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,11 +515,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -595,11 +595,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Parsed Japan unemployment rate from Statistics Bureau latest indicators; period=April 2026.</t>
+          <t>Parsed Japan unemployment rate from Statistics Bureau latest indicators; period=May 2026.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MY</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49.9</v>
+        <v>54.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S&amp;P Global Malaysia Manufacturing PMI via Trading Economics</t>
+          <t>S&amp;P Global Japan Manufacturing PMI via Trading Economics</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Parsed PMI from source; period=May 2026.</t>
+          <t>Parsed PMI from source; period=June 2026.</t>
         </is>
       </c>
     </row>
@@ -1070,35 +1070,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PMI</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54.9</v>
+        <v>1.678445229681969</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>% YoY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S&amp;P Global Japan Manufacturing PMI via Trading Economics</t>
+          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parsed / Secondary</t>
+          <t>Manual official seed</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Parsed PMI from source; period=June 2026.</t>
+          <t>YoY calculated from CPI index by parser</t>
         </is>
       </c>
     </row>
@@ -1115,11 +1115,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.678445229681969</v>
+        <v>1.419698314108242</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1155,11 +1155,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.419698314108242</v>
+        <v>1.591511936339529</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1195,11 +1195,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.591511936339529</v>
+        <v>1.585903083700435</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.585903083700435</v>
+        <v>1.755926251097462</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1270,25 +1270,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inflation</t>
+          <t>Unemployment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.755926251097462</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>% YoY</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Japan Statistics Bureau CPI manual export - All items less imputed rent</t>
+          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>YoY calculated from CPI index by parser</t>
+          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
         </is>
       </c>
     </row>
@@ -1315,11 +1315,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1515,11 +1515,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1595,11 +1595,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1715,11 +1715,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1745,30 +1745,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unemployment</t>
+          <t>Inflation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% YoY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Japan Labour Force Survey manual export - unemployment rate, All Japan, Both sexes</t>
+          <t>SingStat CPI YoY manual export - All Items</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Filtered Labour force status=Unemployed person, Area=All Japan, Sex=Both sexes</t>
+          <t>Percent change in CPI over corresponding period of previous year</t>
         </is>
       </c>
     </row>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1835,11 +1835,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1875,11 +1875,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2075,11 +2075,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2115,11 +2115,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2217,46 +2217,6 @@
         </is>
       </c>
       <c r="H45" t="inlineStr">
-        <is>
-          <t>Percent change in CPI over corresponding period of previous year</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>% YoY</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SingStat CPI YoY manual export - All Items</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Manual official seed</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
         <is>
           <t>Percent change in CPI over corresponding period of previous year</t>
         </is>
@@ -2321,7 +2281,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:16Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2361,7 +2321,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:16Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2385,7 +2345,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2401,7 +2361,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:17Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2441,7 +2401,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:18Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2465,7 +2425,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2481,7 +2441,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:18Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2517,7 +2477,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:18Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2553,7 +2513,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:18Z</t>
+          <t>2026-07-05T09:48:31Z</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2589,7 +2549,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:18Z</t>
+          <t>2026-07-05T09:48:36Z</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2629,7 +2589,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:20Z</t>
+          <t>2026-07-05T09:48:38Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2669,7 +2629,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:22Z</t>
+          <t>2026-07-05T09:48:40Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2707,7 +2667,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:22Z</t>
+          <t>2026-07-05T09:48:40Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2741,7 +2701,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:23Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2781,7 +2741,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:23Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2809,7 +2769,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parsed Japan unemployment 2.5% for April 2026</t>
+          <t>Parsed Japan unemployment 2.5% for May 2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2821,7 +2781,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:23Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,7 +2821,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:23Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2901,7 +2861,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:24Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2941,7 +2901,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:24Z</t>
+          <t>2026-07-05T09:48:41Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2961,15 +2921,13 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>49.9</v>
-      </c>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parsed PMI 49.9 for May 2026</t>
+          <t>Could not parse Malaysia Manufacturing PMI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2981,7 +2939,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:24Z</t>
+          <t>2026-07-05T09:48:42Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3021,7 +2979,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:24Z</t>
+          <t>2026-07-05T09:48:42Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3067,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3095,7 +3053,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:22Z</t>
+          <t>2026-07-05T09:48:40Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3111,6 +3069,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>OpenDOSM unemployment fetch failed: Could not identify unemployment date/value columns; columns=['lf', 'date', 'p_rate', 'u_rate', 'ep_ratio', 'lf_outside', 'lf_employed', 'lf_unemployed']</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-05T09:48:41Z</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PMI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Malaysia PMI parser failed: Could not parse Malaysia Manufacturing PMI</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3557,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-28T00:20:24Z</t>
+          <t>2026-07-05T09:48:42Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
